--- a/data/trans_dic/P34B02_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P34B02_R-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, 3 veces por semana o más</t>
+          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,16</t>
+          <t>2,94; 6,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,56</t>
+          <t>3,81; 7,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,84; 17,86</t>
+          <t>11,03; 17,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,04</t>
+          <t>1,98; 4,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,32</t>
+          <t>2,28; 5,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,46; 14,91</t>
+          <t>10,35; 14,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,06</t>
+          <t>2,88; 5,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 5,7</t>
+          <t>3,28; 5,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,11; 15,16</t>
+          <t>11,27; 15,48</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,13</t>
+          <t>3,48; 6,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 11,34</t>
+          <t>7,33; 11,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,62; 21,26</t>
+          <t>7,53; 21,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,8</t>
+          <t>2,39; 4,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 7,85</t>
+          <t>4,85; 8,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,51; 16,81</t>
+          <t>12,58; 16,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,98</t>
+          <t>3,19; 5,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 9,0</t>
+          <t>6,52; 8,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,29; 17,7</t>
+          <t>10,36; 17,89</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 7,69</t>
+          <t>4,33; 7,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,76</t>
+          <t>4,06; 7,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,35; 26,68</t>
+          <t>17,65; 25,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,62</t>
+          <t>2,75; 5,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,78</t>
+          <t>2,84; 5,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 12,49</t>
+          <t>4,21; 12,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,05</t>
+          <t>3,8; 5,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,12</t>
+          <t>3,87; 6,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,76; 17,53</t>
+          <t>9,31; 17,38</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,28</t>
+          <t>5,08; 8,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,11; 10,82</t>
+          <t>7,1; 10,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,79</t>
+          <t>3,19; 5,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 7,97</t>
+          <t>4,93; 7,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,08; 16,33</t>
+          <t>11,32; 16,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 6,5</t>
+          <t>4,35; 6,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 8,85</t>
+          <t>6,34; 8,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,51; 19,81</t>
+          <t>15,49; 19,68</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 6,25</t>
+          <t>4,66; 6,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,64; 8,53</t>
+          <t>6,66; 8,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,98; 20,41</t>
+          <t>14,31; 20,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 4,53</t>
+          <t>3,19; 4,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,22</t>
+          <t>4,62; 6,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,59; 13,86</t>
+          <t>10,43; 13,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 5,1</t>
+          <t>4,07; 5,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 6,98</t>
+          <t>5,8; 7,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,31; 16,66</t>
+          <t>13,25; 16,7</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, 3 veces por semana o más</t>
+          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21764; 43239</t>
+          <t>20642; 44945</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25896; 51040</t>
+          <t>25694; 50276</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68614; 113050</t>
+          <t>69839; 112798</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15242; 35133</t>
+          <t>13825; 34188</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15420; 35805</t>
+          <t>15312; 34107</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70543; 100526</t>
+          <t>69787; 99223</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40909; 70821</t>
+          <t>40259; 70432</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47074; 76764</t>
+          <t>44173; 76426</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>145277; 198127</t>
+          <t>147352; 202314</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35801; 62425</t>
+          <t>35421; 62607</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74555; 115915</t>
+          <t>74978; 113831</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>102581; 253147</t>
+          <t>89653; 251209</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24945; 49412</t>
+          <t>24610; 50319</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49508; 81871</t>
+          <t>50554; 83947</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>119755; 160950</t>
+          <t>120464; 158664</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65203; 102032</t>
+          <t>65409; 102849</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>134280; 185781</t>
+          <t>134676; 184344</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>221060; 380212</t>
+          <t>222565; 384309</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32187; 58273</t>
+          <t>32767; 58563</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31529; 58930</t>
+          <t>30873; 58352</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>129304; 188031</t>
+          <t>124387; 180667</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21039; 43683</t>
+          <t>21385; 45897</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22073; 45361</t>
+          <t>22327; 46269</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43651; 116568</t>
+          <t>39325; 114778</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>58614; 92808</t>
+          <t>58316; 91777</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>59703; 94582</t>
+          <t>59717; 94678</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>143538; 287177</t>
+          <t>152551; 284590</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47936; 78386</t>
+          <t>48124; 79310</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66617; 101453</t>
+          <t>66611; 102805</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>174553; 234813</t>
+          <t>174613; 234795</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33993; 60895</t>
+          <t>33515; 61248</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50301; 83180</t>
+          <t>51420; 83228</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>120933; 178271</t>
+          <t>123603; 176777</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88899; 129975</t>
+          <t>86942; 128710</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>127431; 175373</t>
+          <t>125595; 173181</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>313141; 399877</t>
+          <t>312613; 397332</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>159461; 213959</t>
+          <t>159752; 213869</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>225471; 289648</t>
+          <t>226105; 291049</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>483064; 704999</t>
+          <t>494412; 704076</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>112404; 160957</t>
+          <t>113574; 163496</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>160398; 220525</t>
+          <t>163789; 217341</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>387261; 506874</t>
+          <t>381246; 510352</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>285254; 356338</t>
+          <t>284181; 358510</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>404184; 484009</t>
+          <t>402679; 485913</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>946294; 1185050</t>
+          <t>941990; 1187365</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B02_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P34B02_R-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,4</t>
+          <t>2,98; 6,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,45</t>
+          <t>3,81; 7,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,03; 17,82</t>
+          <t>10,68; 17,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,9</t>
+          <t>2,24; 5,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,07</t>
+          <t>2,25; 4,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,35; 14,72</t>
+          <t>10,37; 14,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,03</t>
+          <t>2,9; 5,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,67</t>
+          <t>3,42; 5,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 15,48</t>
+          <t>11,32; 15,08</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,15</t>
+          <t>3,38; 6,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,33; 11,13</t>
+          <t>7,39; 11,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 21,1</t>
+          <t>16,37; 22,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,88</t>
+          <t>2,45; 4,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 8,05</t>
+          <t>4,87; 7,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,58; 16,57</t>
+          <t>12,4; 16,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,02</t>
+          <t>3,17; 5,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,93</t>
+          <t>6,44; 8,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,36; 17,89</t>
+          <t>15,26; 18,82</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,73</t>
+          <t>4,3; 7,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,68</t>
+          <t>4,2; 7,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,65; 25,64</t>
+          <t>17,12; 24,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,91</t>
+          <t>2,7; 5,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,89</t>
+          <t>2,91; 5,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 12,3</t>
+          <t>9,64; 13,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,98</t>
+          <t>3,87; 6,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,13</t>
+          <t>3,97; 6,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 17,38</t>
+          <t>14,14; 18,56</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,38</t>
+          <t>4,87; 8,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 10,97</t>
+          <t>7,34; 11,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,84; 25,34</t>
+          <t>20,05; 25,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,82</t>
+          <t>3,18; 5,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,97</t>
+          <t>4,89; 8,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,32; 16,19</t>
+          <t>13,1; 16,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 6,44</t>
+          <t>4,24; 6,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 8,74</t>
+          <t>6,31; 8,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,49; 19,68</t>
+          <t>17,05; 20,58</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 6,24</t>
+          <t>4,63; 6,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,66; 8,57</t>
+          <t>6,65; 8,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,31; 20,38</t>
+          <t>17,99; 21,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 4,6</t>
+          <t>3,16; 4,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,13</t>
+          <t>4,58; 6,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,43; 13,96</t>
+          <t>12,61; 14,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 5,14</t>
+          <t>4,05; 5,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 7,0</t>
+          <t>5,8; 7,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,25; 16,7</t>
+          <t>15,56; 17,41</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87395</t>
+          <t>93244</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84165</t>
+          <t>90680</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>171560</t>
+          <t>183924</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20642; 44945</t>
+          <t>20936; 43654</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25694; 50276</t>
+          <t>25709; 49812</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69839; 112798</t>
+          <t>73447; 118022</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13825; 34188</t>
+          <t>15608; 35821</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15312; 34107</t>
+          <t>15110; 33449</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69787; 99223</t>
+          <t>75867; 107672</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40259; 70432</t>
+          <t>40574; 70405</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44173; 76426</t>
+          <t>46075; 76767</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>147352; 202314</t>
+          <t>160663; 214073</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>187909</t>
+          <t>203534</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>139077</t>
+          <t>154512</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>326985</t>
+          <t>358046</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35421; 62607</t>
+          <t>34382; 62345</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74978; 113831</t>
+          <t>75520; 113676</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89653; 251209</t>
+          <t>171283; 235642</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24610; 50319</t>
+          <t>25213; 50804</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50554; 83947</t>
+          <t>50765; 82527</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>120464; 158664</t>
+          <t>132668; 176438</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65409; 102849</t>
+          <t>64889; 103099</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>134676; 184344</t>
+          <t>132963; 182203</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>222565; 384309</t>
+          <t>322944; 398307</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152641</t>
+          <t>167071</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83833</t>
+          <t>94650</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>236473</t>
+          <t>261721</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32767; 58563</t>
+          <t>32597; 58332</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30873; 58352</t>
+          <t>31896; 58201</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>124387; 180667</t>
+          <t>137463; 194256</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21385; 45897</t>
+          <t>20953; 43215</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22327; 46269</t>
+          <t>22857; 46492</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39325; 114778</t>
+          <t>78105; 112484</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>58316; 91777</t>
+          <t>59387; 94206</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>59717; 94678</t>
+          <t>61330; 95061</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>152551; 284590</t>
+          <t>228040; 299329</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202939</t>
+          <t>225285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>152923</t>
+          <t>165678</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>355862</t>
+          <t>390964</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48124; 79310</t>
+          <t>46076; 78144</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66611; 102805</t>
+          <t>68811; 103542</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>174613; 234795</t>
+          <t>198315; 254027</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33515; 61248</t>
+          <t>33466; 60782</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51420; 83228</t>
+          <t>51012; 84293</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>123603; 176777</t>
+          <t>146344; 188921</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86942; 128710</t>
+          <t>84664; 128048</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>125595; 173181</t>
+          <t>125031; 172879</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>312613; 397332</t>
+          <t>359107; 433428</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>630884</t>
+          <t>689134</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>459998</t>
+          <t>505520</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1090881</t>
+          <t>1194654</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>159752; 213869</t>
+          <t>158657; 210159</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>226105; 291049</t>
+          <t>225886; 290355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>494412; 704076</t>
+          <t>634269; 742774</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>113574; 163496</t>
+          <t>112463; 159792</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>163789; 217341</t>
+          <t>162356; 218899</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>381246; 510352</t>
+          <t>470003; 546123</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>284181; 358510</t>
+          <t>282956; 358909</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>402679; 485913</t>
+          <t>402471; 487216</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>941990; 1187365</t>
+          <t>1128587; 1263093</t>
         </is>
       </c>
     </row>
